--- a/exports/AIDEN_西电课题选题与编组表.xlsx
+++ b/exports/AIDEN_西电课题选题与编组表.xlsx
@@ -642,12 +642,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>群发短稿</t>
+          <t>发群一页稿</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>可直接复制到微信群</t>
+          <t>可直接复制到学生群</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2546,7 +2546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2556,7 +2556,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>微信群发布稿（全选 A 列复制）</t>
+          <t>发群一页稿（全选 A 列复制；正式稿见 Markdown 文件）</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>计划 2026年8月24日（周一） 正式发出。下面十条都是已经开工的真实课题，不是为发榜临时编的。</t>
+          <t>计划 2026年8月24日（周一） 正式发出。下面十条都是已经开工的真实课题。</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>—— 怎么选 ——</t>
+          <t>怎么选</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>—— 十条课题（一句话） ——</t>
+          <t>十条课题</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>状态：已开工，可运行 SPA  ·  3–5 人  ·  12–16 周</t>
+          <t>已开工，可运行 SPA  ·  3–5 人  ·  12–16 周</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>状态：已开工，有演示与蓝图  ·  4–6 人  ·  16 周</t>
+          <t>已开工，有演示与蓝图  ·  4–6 人  ·  16 周</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>状态：已开工，可运行看板  ·  3–5 人  ·  12–16 周</t>
+          <t>已开工，可运行看板  ·  3–5 人  ·  12–16 周</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>状态：规格已完成，待最小原型  ·  3–4 人  ·  12–16 周</t>
+          <t>规格已完成，待最小原型  ·  3–4 人  ·  12–16 周</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>状态：官方 API Skill 已接入  ·  3–5 人  ·  12–16 周</t>
+          <t>官方 API Skill 已接入  ·  3–5 人  ·  12–16 周</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>状态：多份真实材料已产出  ·  3–4 人  ·  12 周</t>
+          <t>多份真实材料已产出  ·  3–4 人  ·  12 周</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>状态：白皮书与展馆方案已出  ·  3–5 人  ·  16 周</t>
+          <t>白皮书与展馆方案已出  ·  3–5 人  ·  16 周</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>状态：看板与研究报告已出  ·  3–4 人  ·  12–16 周</t>
+          <t>看板与研究报告已出  ·  3–4 人  ·  12–16 周</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>状态：主线已在跑，90+ 真实任务  ·  3–5 人  ·  16 周</t>
+          <t>主线已在跑，90+ 真实任务  ·  3–5 人  ·  16 周</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>状态：多份白皮书已出，需持续迭代  ·  4–6 人  ·  16 周</t>
+          <t>多份白皮书已出，需持续迭代  ·  4–6 人  ·  16 周</t>
         </is>
       </c>
     </row>
@@ -2875,67 +2875,46 @@
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>—— 约定 ——</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>进组是做事，不开空证明。远程为主，上海可短期驻场。每周建议不少于 8 小时，有周报。</t>
-        </is>
-      </c>
+          <t>约定：进组做事，不开空证明。远程为主。每周建议不少于 8 小时，有周报。导师不代写。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="8" customHeight="1">
+      <c r="A56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>导师给方向和验收，不代写。密钥、内部名单、个人隐私不进仓库。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="8" customHeight="1">
-      <c r="A58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>—— 请回 ——</t>
-        </is>
-      </c>
+          <t>请回：姓名 ｜ 学院专业年级 ｜ 第一志愿 ｜ 备选 ｜ 每周小时 ｜ 能否赴沪 ｜ 角色意向 ｜ 80字以内我能贡献什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>详细任务见 Word，宣讲见 PPT，填表见 Excel。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="8" customHeight="1">
+      <c r="A59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>姓名 + 学院专业年级 + 第一志愿 + 备选 + 每周小时 + 能否赴沪 + 80 字以内「我能贡献什么」</t>
+          <t>报名入口与对接群由西电侧老师统一发布；本材料只提供课题本身。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>详细任务见 Word，宣讲见 PPT，填表见 Excel。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="8" customHeight="1">
-      <c r="A62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>报名入口与对接群由西电侧老师统一发布；本材料只提供课题本身。</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
           <t>AIDEN 工作组  ·  复旦大学住房政策研究中心  ·  上海市杨浦区科技企业联合会</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>对接：胡继刚  ·  2026年8月20日  ·  V1.0</t>
         </is>
